--- a/data/Briscola_League_Automatica.xlsx
+++ b/data/Briscola_League_Automatica.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\g.pisati\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D3A731F5-BF84-4A4E-B9A8-0199F8D5B2FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E97F3459-098A-4EFE-97B9-4BA6D656BF67}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-20892" yWindow="3900" windowWidth="16200" windowHeight="9312" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-23148" yWindow="1980" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Risultati" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="214" uniqueCount="43">
   <si>
     <t>TORNEO DI BRISCOLA IN CINQUE · 2026–2027</t>
   </si>
@@ -736,8 +736,8 @@
       <c r="A5" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="4" t="s">
-        <v>4</v>
+      <c r="B5" s="4">
+        <v>5</v>
       </c>
       <c r="C5" s="4" t="s">
         <v>4</v>
@@ -777,7 +777,7 @@
       <c r="A6" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="4" t="s">
+      <c r="B6" s="4">
         <v>4</v>
       </c>
       <c r="C6" s="4" t="s">
@@ -818,8 +818,8 @@
       <c r="A7" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B7" s="4" t="s">
-        <v>4</v>
+      <c r="B7" s="4">
+        <v>1</v>
       </c>
       <c r="C7" s="4" t="s">
         <v>4</v>
@@ -900,8 +900,8 @@
       <c r="A9" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B9" s="4" t="s">
-        <v>4</v>
+      <c r="B9" s="4">
+        <v>6</v>
       </c>
       <c r="C9" s="4" t="s">
         <v>4</v>
@@ -982,8 +982,8 @@
       <c r="A11" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="B11" s="4" t="s">
-        <v>4</v>
+      <c r="B11" s="4">
+        <v>2</v>
       </c>
       <c r="C11" s="4" t="s">
         <v>4</v>
@@ -1023,8 +1023,8 @@
       <c r="A12" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="B12" s="4" t="s">
-        <v>4</v>
+      <c r="B12" s="4">
+        <v>7</v>
       </c>
       <c r="C12" s="4" t="s">
         <v>4</v>
@@ -1064,8 +1064,8 @@
       <c r="A13" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="B13" s="4" t="s">
-        <v>4</v>
+      <c r="B13" s="4">
+        <v>3</v>
       </c>
       <c r="C13" s="4" t="s">
         <v>4</v>
@@ -1230,7 +1230,7 @@
       </c>
       <c r="B18" s="7" t="str">
         <f t="shared" ref="B18:M18" si="0">IF(COUNT(B$5:B$15)&gt;=5,"VALIDA","MINIMO 5")</f>
-        <v>MINIMO 5</v>
+        <v>VALIDA</v>
       </c>
       <c r="C18" s="7" t="str">
         <f t="shared" si="0"/>
@@ -1376,16 +1376,16 @@
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A5" s="8" t="str">
-        <f>IF(COUNT(Dettaglio!B5:M5)=0,"—",_xludf.RANK.EQ(J5,$J$5:$J$15,0))</f>
-        <v>—</v>
+      <c r="A5" s="8" t="e">
+        <f ca="1">IF(COUNT(Dettaglio!B5:M5)=0,"—",_xludf.RANK.EQ(J5,$J$5:$J$15,0))</f>
+        <v>#NAME?</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>3</v>
       </c>
       <c r="C5" s="8">
         <f>SUM(IF(COUNT(Risultati!B$5:B$15)&gt;=5,IF(ISNUMBER(Risultati!B5),1,0),0),IF(COUNT(Risultati!C$5:C$15)&gt;=5,IF(ISNUMBER(Risultati!C5),1,0),0),IF(COUNT(Risultati!D$5:D$15)&gt;=5,IF(ISNUMBER(Risultati!D5),1,0),0),IF(COUNT(Risultati!E$5:E$15)&gt;=5,IF(ISNUMBER(Risultati!E5),1,0),0),IF(COUNT(Risultati!F$5:F$15)&gt;=5,IF(ISNUMBER(Risultati!F5),1,0),0),IF(COUNT(Risultati!G$5:G$15)&gt;=5,IF(ISNUMBER(Risultati!G5),1,0),0),IF(COUNT(Risultati!H$5:H$15)&gt;=5,IF(ISNUMBER(Risultati!H5),1,0),0),IF(COUNT(Risultati!I$5:I$15)&gt;=5,IF(ISNUMBER(Risultati!I5),1,0),0),IF(COUNT(Risultati!J$5:J$15)&gt;=5,IF(ISNUMBER(Risultati!J5),1,0),0),IF(COUNT(Risultati!K$5:K$15)&gt;=5,IF(ISNUMBER(Risultati!K5),1,0),0),IF(COUNT(Risultati!L$5:L$15)&gt;=5,IF(ISNUMBER(Risultati!L5),1,0),0),IF(COUNT(Risultati!M$5:M$15)&gt;=5,IF(ISNUMBER(Risultati!M5),1,0),0))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D5" s="8">
         <f>SUM(IF(COUNT(Risultati!B$5:B$15)&gt;=5,IF(Risultati!B5=1,1,0),0),IF(COUNT(Risultati!C$5:C$15)&gt;=5,IF(Risultati!C5=1,1,0),0),IF(COUNT(Risultati!D$5:D$15)&gt;=5,IF(Risultati!D5=1,1,0),0),IF(COUNT(Risultati!E$5:E$15)&gt;=5,IF(Risultati!E5=1,1,0),0),IF(COUNT(Risultati!F$5:F$15)&gt;=5,IF(Risultati!F5=1,1,0),0),IF(COUNT(Risultati!G$5:G$15)&gt;=5,IF(Risultati!G5=1,1,0),0),IF(COUNT(Risultati!H$5:H$15)&gt;=5,IF(Risultati!H5=1,1,0),0),IF(COUNT(Risultati!I$5:I$15)&gt;=5,IF(Risultati!I5=1,1,0),0),IF(COUNT(Risultati!J$5:J$15)&gt;=5,IF(Risultati!J5=1,1,0),0),IF(COUNT(Risultati!K$5:K$15)&gt;=5,IF(Risultati!K5=1,1,0),0),IF(COUNT(Risultati!L$5:L$15)&gt;=5,IF(Risultati!L5=1,1,0),0),IF(COUNT(Risultati!M$5:M$15)&gt;=5,IF(Risultati!M5=1,1,0),0))</f>
@@ -1401,11 +1401,11 @@
       </c>
       <c r="G5" s="8">
         <f>SUM(Dettaglio!B5:M5)</f>
-        <v>0</v>
-      </c>
-      <c r="H5" s="8" t="str">
+        <v>15</v>
+      </c>
+      <c r="H5" s="8">
         <f>IF(COUNT(Dettaglio!B5:M5)=0,"—",SMALL(Dettaglio!B5:M5,1))</f>
-        <v>—</v>
+        <v>15</v>
       </c>
       <c r="I5" s="8" t="str">
         <f>IF(COUNT(Dettaglio!B5:M5)&lt;2,"—",SMALL(Dettaglio!B5:M5,2))</f>
@@ -1417,16 +1417,16 @@
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A6" s="8" t="str">
-        <f>IF(COUNT(Dettaglio!B6:M6)=0,"—",_xludf.RANK.EQ(J6,$J$5:$J$15,0))</f>
-        <v>—</v>
+      <c r="A6" s="8" t="e">
+        <f ca="1">IF(COUNT(Dettaglio!B6:M6)=0,"—",_xludf.RANK.EQ(J6,$J$5:$J$15,0))</f>
+        <v>#NAME?</v>
       </c>
       <c r="B6" s="3" t="s">
         <v>5</v>
       </c>
       <c r="C6" s="8">
         <f>SUM(IF(COUNT(Risultati!B$5:B$15)&gt;=5,IF(ISNUMBER(Risultati!B6),1,0),0),IF(COUNT(Risultati!C$5:C$15)&gt;=5,IF(ISNUMBER(Risultati!C6),1,0),0),IF(COUNT(Risultati!D$5:D$15)&gt;=5,IF(ISNUMBER(Risultati!D6),1,0),0),IF(COUNT(Risultati!E$5:E$15)&gt;=5,IF(ISNUMBER(Risultati!E6),1,0),0),IF(COUNT(Risultati!F$5:F$15)&gt;=5,IF(ISNUMBER(Risultati!F6),1,0),0),IF(COUNT(Risultati!G$5:G$15)&gt;=5,IF(ISNUMBER(Risultati!G6),1,0),0),IF(COUNT(Risultati!H$5:H$15)&gt;=5,IF(ISNUMBER(Risultati!H6),1,0),0),IF(COUNT(Risultati!I$5:I$15)&gt;=5,IF(ISNUMBER(Risultati!I6),1,0),0),IF(COUNT(Risultati!J$5:J$15)&gt;=5,IF(ISNUMBER(Risultati!J6),1,0),0),IF(COUNT(Risultati!K$5:K$15)&gt;=5,IF(ISNUMBER(Risultati!K6),1,0),0),IF(COUNT(Risultati!L$5:L$15)&gt;=5,IF(ISNUMBER(Risultati!L6),1,0),0),IF(COUNT(Risultati!M$5:M$15)&gt;=5,IF(ISNUMBER(Risultati!M6),1,0),0))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D6" s="8">
         <f>SUM(IF(COUNT(Risultati!B$5:B$15)&gt;=5,IF(Risultati!B6=1,1,0),0),IF(COUNT(Risultati!C$5:C$15)&gt;=5,IF(Risultati!C6=1,1,0),0),IF(COUNT(Risultati!D$5:D$15)&gt;=5,IF(Risultati!D6=1,1,0),0),IF(COUNT(Risultati!E$5:E$15)&gt;=5,IF(Risultati!E6=1,1,0),0),IF(COUNT(Risultati!F$5:F$15)&gt;=5,IF(Risultati!F6=1,1,0),0),IF(COUNT(Risultati!G$5:G$15)&gt;=5,IF(Risultati!G6=1,1,0),0),IF(COUNT(Risultati!H$5:H$15)&gt;=5,IF(Risultati!H6=1,1,0),0),IF(COUNT(Risultati!I$5:I$15)&gt;=5,IF(Risultati!I6=1,1,0),0),IF(COUNT(Risultati!J$5:J$15)&gt;=5,IF(Risultati!J6=1,1,0),0),IF(COUNT(Risultati!K$5:K$15)&gt;=5,IF(Risultati!K6=1,1,0),0),IF(COUNT(Risultati!L$5:L$15)&gt;=5,IF(Risultati!L6=1,1,0),0),IF(COUNT(Risultati!M$5:M$15)&gt;=5,IF(Risultati!M6=1,1,0),0))</f>
@@ -1442,11 +1442,11 @@
       </c>
       <c r="G6" s="8">
         <f>SUM(Dettaglio!B6:M6)</f>
-        <v>0</v>
-      </c>
-      <c r="H6" s="8" t="str">
+        <v>17</v>
+      </c>
+      <c r="H6" s="8">
         <f>IF(COUNT(Dettaglio!B6:M6)=0,"—",SMALL(Dettaglio!B6:M6,1))</f>
-        <v>—</v>
+        <v>17</v>
       </c>
       <c r="I6" s="8" t="str">
         <f>IF(COUNT(Dettaglio!B6:M6)&lt;2,"—",SMALL(Dettaglio!B6:M6,2))</f>
@@ -1458,20 +1458,20 @@
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A7" s="8" t="str">
-        <f>IF(COUNT(Dettaglio!B7:M7)=0,"—",_xludf.RANK.EQ(J7,$J$5:$J$15,0))</f>
-        <v>—</v>
+      <c r="A7" s="8" t="e">
+        <f ca="1">IF(COUNT(Dettaglio!B7:M7)=0,"—",_xludf.RANK.EQ(J7,$J$5:$J$15,0))</f>
+        <v>#NAME?</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>6</v>
       </c>
       <c r="C7" s="8">
         <f>SUM(IF(COUNT(Risultati!B$5:B$15)&gt;=5,IF(ISNUMBER(Risultati!B7),1,0),0),IF(COUNT(Risultati!C$5:C$15)&gt;=5,IF(ISNUMBER(Risultati!C7),1,0),0),IF(COUNT(Risultati!D$5:D$15)&gt;=5,IF(ISNUMBER(Risultati!D7),1,0),0),IF(COUNT(Risultati!E$5:E$15)&gt;=5,IF(ISNUMBER(Risultati!E7),1,0),0),IF(COUNT(Risultati!F$5:F$15)&gt;=5,IF(ISNUMBER(Risultati!F7),1,0),0),IF(COUNT(Risultati!G$5:G$15)&gt;=5,IF(ISNUMBER(Risultati!G7),1,0),0),IF(COUNT(Risultati!H$5:H$15)&gt;=5,IF(ISNUMBER(Risultati!H7),1,0),0),IF(COUNT(Risultati!I$5:I$15)&gt;=5,IF(ISNUMBER(Risultati!I7),1,0),0),IF(COUNT(Risultati!J$5:J$15)&gt;=5,IF(ISNUMBER(Risultati!J7),1,0),0),IF(COUNT(Risultati!K$5:K$15)&gt;=5,IF(ISNUMBER(Risultati!K7),1,0),0),IF(COUNT(Risultati!L$5:L$15)&gt;=5,IF(ISNUMBER(Risultati!L7),1,0),0),IF(COUNT(Risultati!M$5:M$15)&gt;=5,IF(ISNUMBER(Risultati!M7),1,0),0))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D7" s="8">
         <f>SUM(IF(COUNT(Risultati!B$5:B$15)&gt;=5,IF(Risultati!B7=1,1,0),0),IF(COUNT(Risultati!C$5:C$15)&gt;=5,IF(Risultati!C7=1,1,0),0),IF(COUNT(Risultati!D$5:D$15)&gt;=5,IF(Risultati!D7=1,1,0),0),IF(COUNT(Risultati!E$5:E$15)&gt;=5,IF(Risultati!E7=1,1,0),0),IF(COUNT(Risultati!F$5:F$15)&gt;=5,IF(Risultati!F7=1,1,0),0),IF(COUNT(Risultati!G$5:G$15)&gt;=5,IF(Risultati!G7=1,1,0),0),IF(COUNT(Risultati!H$5:H$15)&gt;=5,IF(Risultati!H7=1,1,0),0),IF(COUNT(Risultati!I$5:I$15)&gt;=5,IF(Risultati!I7=1,1,0),0),IF(COUNT(Risultati!J$5:J$15)&gt;=5,IF(Risultati!J7=1,1,0),0),IF(COUNT(Risultati!K$5:K$15)&gt;=5,IF(Risultati!K7=1,1,0),0),IF(COUNT(Risultati!L$5:L$15)&gt;=5,IF(Risultati!L7=1,1,0),0),IF(COUNT(Risultati!M$5:M$15)&gt;=5,IF(Risultati!M7=1,1,0),0))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E7" s="8">
         <f>SUM(IF(COUNT(Risultati!B$5:B$15)&gt;=5,IF(Risultati!B7=2,1,0),0),IF(COUNT(Risultati!C$5:C$15)&gt;=5,IF(Risultati!C7=2,1,0),0),IF(COUNT(Risultati!D$5:D$15)&gt;=5,IF(Risultati!D7=2,1,0),0),IF(COUNT(Risultati!E$5:E$15)&gt;=5,IF(Risultati!E7=2,1,0),0),IF(COUNT(Risultati!F$5:F$15)&gt;=5,IF(Risultati!F7=2,1,0),0),IF(COUNT(Risultati!G$5:G$15)&gt;=5,IF(Risultati!G7=2,1,0),0),IF(COUNT(Risultati!H$5:H$15)&gt;=5,IF(Risultati!H7=2,1,0),0),IF(COUNT(Risultati!I$5:I$15)&gt;=5,IF(Risultati!I7=2,1,0),0),IF(COUNT(Risultati!J$5:J$15)&gt;=5,IF(Risultati!J7=2,1,0),0),IF(COUNT(Risultati!K$5:K$15)&gt;=5,IF(Risultati!K7=2,1,0),0),IF(COUNT(Risultati!L$5:L$15)&gt;=5,IF(Risultati!L7=2,1,0),0),IF(COUNT(Risultati!M$5:M$15)&gt;=5,IF(Risultati!M7=2,1,0),0))</f>
@@ -1483,11 +1483,11 @@
       </c>
       <c r="G7" s="8">
         <f>SUM(Dettaglio!B7:M7)</f>
-        <v>0</v>
-      </c>
-      <c r="H7" s="8" t="str">
+        <v>30</v>
+      </c>
+      <c r="H7" s="8">
         <f>IF(COUNT(Dettaglio!B7:M7)=0,"—",SMALL(Dettaglio!B7:M7,1))</f>
-        <v>—</v>
+        <v>30</v>
       </c>
       <c r="I7" s="8" t="str">
         <f>IF(COUNT(Dettaglio!B7:M7)&lt;2,"—",SMALL(Dettaglio!B7:M7,2))</f>
@@ -1499,9 +1499,9 @@
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A8" s="8" t="str">
-        <f>IF(COUNT(Dettaglio!B8:M8)=0,"—",_xludf.RANK.EQ(J8,$J$5:$J$15,0))</f>
-        <v>—</v>
+      <c r="A8" s="8" t="e">
+        <f ca="1">IF(COUNT(Dettaglio!B8:M8)=0,"—",_xludf.RANK.EQ(J8,$J$5:$J$15,0))</f>
+        <v>#NAME?</v>
       </c>
       <c r="B8" s="3" t="s">
         <v>7</v>
@@ -1526,9 +1526,9 @@
         <f>SUM(Dettaglio!B8:M8)</f>
         <v>0</v>
       </c>
-      <c r="H8" s="8" t="str">
+      <c r="H8" s="8">
         <f>IF(COUNT(Dettaglio!B8:M8)=0,"—",SMALL(Dettaglio!B8:M8,1))</f>
-        <v>—</v>
+        <v>0</v>
       </c>
       <c r="I8" s="8" t="str">
         <f>IF(COUNT(Dettaglio!B8:M8)&lt;2,"—",SMALL(Dettaglio!B8:M8,2))</f>
@@ -1540,16 +1540,16 @@
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A9" s="8" t="str">
-        <f>IF(COUNT(Dettaglio!B9:M9)=0,"—",_xludf.RANK.EQ(J9,$J$5:$J$15,0))</f>
-        <v>—</v>
+      <c r="A9" s="8" t="e">
+        <f ca="1">IF(COUNT(Dettaglio!B9:M9)=0,"—",_xludf.RANK.EQ(J9,$J$5:$J$15,0))</f>
+        <v>#NAME?</v>
       </c>
       <c r="B9" s="3" t="s">
         <v>8</v>
       </c>
       <c r="C9" s="8">
         <f>SUM(IF(COUNT(Risultati!B$5:B$15)&gt;=5,IF(ISNUMBER(Risultati!B9),1,0),0),IF(COUNT(Risultati!C$5:C$15)&gt;=5,IF(ISNUMBER(Risultati!C9),1,0),0),IF(COUNT(Risultati!D$5:D$15)&gt;=5,IF(ISNUMBER(Risultati!D9),1,0),0),IF(COUNT(Risultati!E$5:E$15)&gt;=5,IF(ISNUMBER(Risultati!E9),1,0),0),IF(COUNT(Risultati!F$5:F$15)&gt;=5,IF(ISNUMBER(Risultati!F9),1,0),0),IF(COUNT(Risultati!G$5:G$15)&gt;=5,IF(ISNUMBER(Risultati!G9),1,0),0),IF(COUNT(Risultati!H$5:H$15)&gt;=5,IF(ISNUMBER(Risultati!H9),1,0),0),IF(COUNT(Risultati!I$5:I$15)&gt;=5,IF(ISNUMBER(Risultati!I9),1,0),0),IF(COUNT(Risultati!J$5:J$15)&gt;=5,IF(ISNUMBER(Risultati!J9),1,0),0),IF(COUNT(Risultati!K$5:K$15)&gt;=5,IF(ISNUMBER(Risultati!K9),1,0),0),IF(COUNT(Risultati!L$5:L$15)&gt;=5,IF(ISNUMBER(Risultati!L9),1,0),0),IF(COUNT(Risultati!M$5:M$15)&gt;=5,IF(ISNUMBER(Risultati!M9),1,0),0))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D9" s="8">
         <f>SUM(IF(COUNT(Risultati!B$5:B$15)&gt;=5,IF(Risultati!B9=1,1,0),0),IF(COUNT(Risultati!C$5:C$15)&gt;=5,IF(Risultati!C9=1,1,0),0),IF(COUNT(Risultati!D$5:D$15)&gt;=5,IF(Risultati!D9=1,1,0),0),IF(COUNT(Risultati!E$5:E$15)&gt;=5,IF(Risultati!E9=1,1,0),0),IF(COUNT(Risultati!F$5:F$15)&gt;=5,IF(Risultati!F9=1,1,0),0),IF(COUNT(Risultati!G$5:G$15)&gt;=5,IF(Risultati!G9=1,1,0),0),IF(COUNT(Risultati!H$5:H$15)&gt;=5,IF(Risultati!H9=1,1,0),0),IF(COUNT(Risultati!I$5:I$15)&gt;=5,IF(Risultati!I9=1,1,0),0),IF(COUNT(Risultati!J$5:J$15)&gt;=5,IF(Risultati!J9=1,1,0),0),IF(COUNT(Risultati!K$5:K$15)&gt;=5,IF(Risultati!K9=1,1,0),0),IF(COUNT(Risultati!L$5:L$15)&gt;=5,IF(Risultati!L9=1,1,0),0),IF(COUNT(Risultati!M$5:M$15)&gt;=5,IF(Risultati!M9=1,1,0),0))</f>
@@ -1565,11 +1565,11 @@
       </c>
       <c r="G9" s="8">
         <f>SUM(Dettaglio!B9:M9)</f>
-        <v>0</v>
-      </c>
-      <c r="H9" s="8" t="str">
+        <v>13</v>
+      </c>
+      <c r="H9" s="8">
         <f>IF(COUNT(Dettaglio!B9:M9)=0,"—",SMALL(Dettaglio!B9:M9,1))</f>
-        <v>—</v>
+        <v>13</v>
       </c>
       <c r="I9" s="8" t="str">
         <f>IF(COUNT(Dettaglio!B9:M9)&lt;2,"—",SMALL(Dettaglio!B9:M9,2))</f>
@@ -1581,9 +1581,9 @@
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A10" s="8" t="str">
-        <f>IF(COUNT(Dettaglio!B10:M10)=0,"—",_xludf.RANK.EQ(J10,$J$5:$J$15,0))</f>
-        <v>—</v>
+      <c r="A10" s="8" t="e">
+        <f ca="1">IF(COUNT(Dettaglio!B10:M10)=0,"—",_xludf.RANK.EQ(J10,$J$5:$J$15,0))</f>
+        <v>#NAME?</v>
       </c>
       <c r="B10" s="3" t="s">
         <v>9</v>
@@ -1608,9 +1608,9 @@
         <f>SUM(Dettaglio!B10:M10)</f>
         <v>0</v>
       </c>
-      <c r="H10" s="8" t="str">
+      <c r="H10" s="8">
         <f>IF(COUNT(Dettaglio!B10:M10)=0,"—",SMALL(Dettaglio!B10:M10,1))</f>
-        <v>—</v>
+        <v>0</v>
       </c>
       <c r="I10" s="8" t="str">
         <f>IF(COUNT(Dettaglio!B10:M10)&lt;2,"—",SMALL(Dettaglio!B10:M10,2))</f>
@@ -1622,16 +1622,16 @@
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A11" s="8" t="str">
-        <f>IF(COUNT(Dettaglio!B11:M11)=0,"—",_xludf.RANK.EQ(J11,$J$5:$J$15,0))</f>
-        <v>—</v>
+      <c r="A11" s="8" t="e">
+        <f ca="1">IF(COUNT(Dettaglio!B11:M11)=0,"—",_xludf.RANK.EQ(J11,$J$5:$J$15,0))</f>
+        <v>#NAME?</v>
       </c>
       <c r="B11" s="3" t="s">
         <v>10</v>
       </c>
       <c r="C11" s="8">
         <f>SUM(IF(COUNT(Risultati!B$5:B$15)&gt;=5,IF(ISNUMBER(Risultati!B11),1,0),0),IF(COUNT(Risultati!C$5:C$15)&gt;=5,IF(ISNUMBER(Risultati!C11),1,0),0),IF(COUNT(Risultati!D$5:D$15)&gt;=5,IF(ISNUMBER(Risultati!D11),1,0),0),IF(COUNT(Risultati!E$5:E$15)&gt;=5,IF(ISNUMBER(Risultati!E11),1,0),0),IF(COUNT(Risultati!F$5:F$15)&gt;=5,IF(ISNUMBER(Risultati!F11),1,0),0),IF(COUNT(Risultati!G$5:G$15)&gt;=5,IF(ISNUMBER(Risultati!G11),1,0),0),IF(COUNT(Risultati!H$5:H$15)&gt;=5,IF(ISNUMBER(Risultati!H11),1,0),0),IF(COUNT(Risultati!I$5:I$15)&gt;=5,IF(ISNUMBER(Risultati!I11),1,0),0),IF(COUNT(Risultati!J$5:J$15)&gt;=5,IF(ISNUMBER(Risultati!J11),1,0),0),IF(COUNT(Risultati!K$5:K$15)&gt;=5,IF(ISNUMBER(Risultati!K11),1,0),0),IF(COUNT(Risultati!L$5:L$15)&gt;=5,IF(ISNUMBER(Risultati!L11),1,0),0),IF(COUNT(Risultati!M$5:M$15)&gt;=5,IF(ISNUMBER(Risultati!M11),1,0),0))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D11" s="8">
         <f>SUM(IF(COUNT(Risultati!B$5:B$15)&gt;=5,IF(Risultati!B11=1,1,0),0),IF(COUNT(Risultati!C$5:C$15)&gt;=5,IF(Risultati!C11=1,1,0),0),IF(COUNT(Risultati!D$5:D$15)&gt;=5,IF(Risultati!D11=1,1,0),0),IF(COUNT(Risultati!E$5:E$15)&gt;=5,IF(Risultati!E11=1,1,0),0),IF(COUNT(Risultati!F$5:F$15)&gt;=5,IF(Risultati!F11=1,1,0),0),IF(COUNT(Risultati!G$5:G$15)&gt;=5,IF(Risultati!G11=1,1,0),0),IF(COUNT(Risultati!H$5:H$15)&gt;=5,IF(Risultati!H11=1,1,0),0),IF(COUNT(Risultati!I$5:I$15)&gt;=5,IF(Risultati!I11=1,1,0),0),IF(COUNT(Risultati!J$5:J$15)&gt;=5,IF(Risultati!J11=1,1,0),0),IF(COUNT(Risultati!K$5:K$15)&gt;=5,IF(Risultati!K11=1,1,0),0),IF(COUNT(Risultati!L$5:L$15)&gt;=5,IF(Risultati!L11=1,1,0),0),IF(COUNT(Risultati!M$5:M$15)&gt;=5,IF(Risultati!M11=1,1,0),0))</f>
@@ -1639,7 +1639,7 @@
       </c>
       <c r="E11" s="8">
         <f>SUM(IF(COUNT(Risultati!B$5:B$15)&gt;=5,IF(Risultati!B11=2,1,0),0),IF(COUNT(Risultati!C$5:C$15)&gt;=5,IF(Risultati!C11=2,1,0),0),IF(COUNT(Risultati!D$5:D$15)&gt;=5,IF(Risultati!D11=2,1,0),0),IF(COUNT(Risultati!E$5:E$15)&gt;=5,IF(Risultati!E11=2,1,0),0),IF(COUNT(Risultati!F$5:F$15)&gt;=5,IF(Risultati!F11=2,1,0),0),IF(COUNT(Risultati!G$5:G$15)&gt;=5,IF(Risultati!G11=2,1,0),0),IF(COUNT(Risultati!H$5:H$15)&gt;=5,IF(Risultati!H11=2,1,0),0),IF(COUNT(Risultati!I$5:I$15)&gt;=5,IF(Risultati!I11=2,1,0),0),IF(COUNT(Risultati!J$5:J$15)&gt;=5,IF(Risultati!J11=2,1,0),0),IF(COUNT(Risultati!K$5:K$15)&gt;=5,IF(Risultati!K11=2,1,0),0),IF(COUNT(Risultati!L$5:L$15)&gt;=5,IF(Risultati!L11=2,1,0),0),IF(COUNT(Risultati!M$5:M$15)&gt;=5,IF(Risultati!M11=2,1,0),0))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F11" s="8">
         <f>SUM(IF(COUNT(Risultati!B$5:B$15)&gt;=5,IF(Risultati!B11=3,1,0),0),IF(COUNT(Risultati!C$5:C$15)&gt;=5,IF(Risultati!C11=3,1,0),0),IF(COUNT(Risultati!D$5:D$15)&gt;=5,IF(Risultati!D11=3,1,0),0),IF(COUNT(Risultati!E$5:E$15)&gt;=5,IF(Risultati!E11=3,1,0),0),IF(COUNT(Risultati!F$5:F$15)&gt;=5,IF(Risultati!F11=3,1,0),0),IF(COUNT(Risultati!G$5:G$15)&gt;=5,IF(Risultati!G11=3,1,0),0),IF(COUNT(Risultati!H$5:H$15)&gt;=5,IF(Risultati!H11=3,1,0),0),IF(COUNT(Risultati!I$5:I$15)&gt;=5,IF(Risultati!I11=3,1,0),0),IF(COUNT(Risultati!J$5:J$15)&gt;=5,IF(Risultati!J11=3,1,0),0),IF(COUNT(Risultati!K$5:K$15)&gt;=5,IF(Risultati!K11=3,1,0),0),IF(COUNT(Risultati!L$5:L$15)&gt;=5,IF(Risultati!L11=3,1,0),0),IF(COUNT(Risultati!M$5:M$15)&gt;=5,IF(Risultati!M11=3,1,0),0))</f>
@@ -1647,11 +1647,11 @@
       </c>
       <c r="G11" s="8">
         <f>SUM(Dettaglio!B11:M11)</f>
-        <v>0</v>
-      </c>
-      <c r="H11" s="8" t="str">
+        <v>23</v>
+      </c>
+      <c r="H11" s="8">
         <f>IF(COUNT(Dettaglio!B11:M11)=0,"—",SMALL(Dettaglio!B11:M11,1))</f>
-        <v>—</v>
+        <v>23</v>
       </c>
       <c r="I11" s="8" t="str">
         <f>IF(COUNT(Dettaglio!B11:M11)&lt;2,"—",SMALL(Dettaglio!B11:M11,2))</f>
@@ -1663,16 +1663,16 @@
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A12" s="8" t="str">
-        <f>IF(COUNT(Dettaglio!B12:M12)=0,"—",_xludf.RANK.EQ(J12,$J$5:$J$15,0))</f>
-        <v>—</v>
+      <c r="A12" s="8" t="e">
+        <f ca="1">IF(COUNT(Dettaglio!B12:M12)=0,"—",_xludf.RANK.EQ(J12,$J$5:$J$15,0))</f>
+        <v>#NAME?</v>
       </c>
       <c r="B12" s="3" t="s">
         <v>11</v>
       </c>
       <c r="C12" s="8">
         <f>SUM(IF(COUNT(Risultati!B$5:B$15)&gt;=5,IF(ISNUMBER(Risultati!B12),1,0),0),IF(COUNT(Risultati!C$5:C$15)&gt;=5,IF(ISNUMBER(Risultati!C12),1,0),0),IF(COUNT(Risultati!D$5:D$15)&gt;=5,IF(ISNUMBER(Risultati!D12),1,0),0),IF(COUNT(Risultati!E$5:E$15)&gt;=5,IF(ISNUMBER(Risultati!E12),1,0),0),IF(COUNT(Risultati!F$5:F$15)&gt;=5,IF(ISNUMBER(Risultati!F12),1,0),0),IF(COUNT(Risultati!G$5:G$15)&gt;=5,IF(ISNUMBER(Risultati!G12),1,0),0),IF(COUNT(Risultati!H$5:H$15)&gt;=5,IF(ISNUMBER(Risultati!H12),1,0),0),IF(COUNT(Risultati!I$5:I$15)&gt;=5,IF(ISNUMBER(Risultati!I12),1,0),0),IF(COUNT(Risultati!J$5:J$15)&gt;=5,IF(ISNUMBER(Risultati!J12),1,0),0),IF(COUNT(Risultati!K$5:K$15)&gt;=5,IF(ISNUMBER(Risultati!K12),1,0),0),IF(COUNT(Risultati!L$5:L$15)&gt;=5,IF(ISNUMBER(Risultati!L12),1,0),0),IF(COUNT(Risultati!M$5:M$15)&gt;=5,IF(ISNUMBER(Risultati!M12),1,0),0))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D12" s="8">
         <f>SUM(IF(COUNT(Risultati!B$5:B$15)&gt;=5,IF(Risultati!B12=1,1,0),0),IF(COUNT(Risultati!C$5:C$15)&gt;=5,IF(Risultati!C12=1,1,0),0),IF(COUNT(Risultati!D$5:D$15)&gt;=5,IF(Risultati!D12=1,1,0),0),IF(COUNT(Risultati!E$5:E$15)&gt;=5,IF(Risultati!E12=1,1,0),0),IF(COUNT(Risultati!F$5:F$15)&gt;=5,IF(Risultati!F12=1,1,0),0),IF(COUNT(Risultati!G$5:G$15)&gt;=5,IF(Risultati!G12=1,1,0),0),IF(COUNT(Risultati!H$5:H$15)&gt;=5,IF(Risultati!H12=1,1,0),0),IF(COUNT(Risultati!I$5:I$15)&gt;=5,IF(Risultati!I12=1,1,0),0),IF(COUNT(Risultati!J$5:J$15)&gt;=5,IF(Risultati!J12=1,1,0),0),IF(COUNT(Risultati!K$5:K$15)&gt;=5,IF(Risultati!K12=1,1,0),0),IF(COUNT(Risultati!L$5:L$15)&gt;=5,IF(Risultati!L12=1,1,0),0),IF(COUNT(Risultati!M$5:M$15)&gt;=5,IF(Risultati!M12=1,1,0),0))</f>
@@ -1688,11 +1688,11 @@
       </c>
       <c r="G12" s="8">
         <f>SUM(Dettaglio!B12:M12)</f>
-        <v>0</v>
-      </c>
-      <c r="H12" s="8" t="str">
+        <v>11</v>
+      </c>
+      <c r="H12" s="8">
         <f>IF(COUNT(Dettaglio!B12:M12)=0,"—",SMALL(Dettaglio!B12:M12,1))</f>
-        <v>—</v>
+        <v>11</v>
       </c>
       <c r="I12" s="8" t="str">
         <f>IF(COUNT(Dettaglio!B12:M12)&lt;2,"—",SMALL(Dettaglio!B12:M12,2))</f>
@@ -1704,16 +1704,16 @@
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A13" s="8" t="str">
-        <f>IF(COUNT(Dettaglio!B13:M13)=0,"—",_xludf.RANK.EQ(J13,$J$5:$J$15,0))</f>
-        <v>—</v>
+      <c r="A13" s="8" t="e">
+        <f ca="1">IF(COUNT(Dettaglio!B13:M13)=0,"—",_xludf.RANK.EQ(J13,$J$5:$J$15,0))</f>
+        <v>#NAME?</v>
       </c>
       <c r="B13" s="3" t="s">
         <v>12</v>
       </c>
       <c r="C13" s="8">
         <f>SUM(IF(COUNT(Risultati!B$5:B$15)&gt;=5,IF(ISNUMBER(Risultati!B13),1,0),0),IF(COUNT(Risultati!C$5:C$15)&gt;=5,IF(ISNUMBER(Risultati!C13),1,0),0),IF(COUNT(Risultati!D$5:D$15)&gt;=5,IF(ISNUMBER(Risultati!D13),1,0),0),IF(COUNT(Risultati!E$5:E$15)&gt;=5,IF(ISNUMBER(Risultati!E13),1,0),0),IF(COUNT(Risultati!F$5:F$15)&gt;=5,IF(ISNUMBER(Risultati!F13),1,0),0),IF(COUNT(Risultati!G$5:G$15)&gt;=5,IF(ISNUMBER(Risultati!G13),1,0),0),IF(COUNT(Risultati!H$5:H$15)&gt;=5,IF(ISNUMBER(Risultati!H13),1,0),0),IF(COUNT(Risultati!I$5:I$15)&gt;=5,IF(ISNUMBER(Risultati!I13),1,0),0),IF(COUNT(Risultati!J$5:J$15)&gt;=5,IF(ISNUMBER(Risultati!J13),1,0),0),IF(COUNT(Risultati!K$5:K$15)&gt;=5,IF(ISNUMBER(Risultati!K13),1,0),0),IF(COUNT(Risultati!L$5:L$15)&gt;=5,IF(ISNUMBER(Risultati!L13),1,0),0),IF(COUNT(Risultati!M$5:M$15)&gt;=5,IF(ISNUMBER(Risultati!M13),1,0),0))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D13" s="8">
         <f>SUM(IF(COUNT(Risultati!B$5:B$15)&gt;=5,IF(Risultati!B13=1,1,0),0),IF(COUNT(Risultati!C$5:C$15)&gt;=5,IF(Risultati!C13=1,1,0),0),IF(COUNT(Risultati!D$5:D$15)&gt;=5,IF(Risultati!D13=1,1,0),0),IF(COUNT(Risultati!E$5:E$15)&gt;=5,IF(Risultati!E13=1,1,0),0),IF(COUNT(Risultati!F$5:F$15)&gt;=5,IF(Risultati!F13=1,1,0),0),IF(COUNT(Risultati!G$5:G$15)&gt;=5,IF(Risultati!G13=1,1,0),0),IF(COUNT(Risultati!H$5:H$15)&gt;=5,IF(Risultati!H13=1,1,0),0),IF(COUNT(Risultati!I$5:I$15)&gt;=5,IF(Risultati!I13=1,1,0),0),IF(COUNT(Risultati!J$5:J$15)&gt;=5,IF(Risultati!J13=1,1,0),0),IF(COUNT(Risultati!K$5:K$15)&gt;=5,IF(Risultati!K13=1,1,0),0),IF(COUNT(Risultati!L$5:L$15)&gt;=5,IF(Risultati!L13=1,1,0),0),IF(COUNT(Risultati!M$5:M$15)&gt;=5,IF(Risultati!M13=1,1,0),0))</f>
@@ -1725,15 +1725,15 @@
       </c>
       <c r="F13" s="8">
         <f>SUM(IF(COUNT(Risultati!B$5:B$15)&gt;=5,IF(Risultati!B13=3,1,0),0),IF(COUNT(Risultati!C$5:C$15)&gt;=5,IF(Risultati!C13=3,1,0),0),IF(COUNT(Risultati!D$5:D$15)&gt;=5,IF(Risultati!D13=3,1,0),0),IF(COUNT(Risultati!E$5:E$15)&gt;=5,IF(Risultati!E13=3,1,0),0),IF(COUNT(Risultati!F$5:F$15)&gt;=5,IF(Risultati!F13=3,1,0),0),IF(COUNT(Risultati!G$5:G$15)&gt;=5,IF(Risultati!G13=3,1,0),0),IF(COUNT(Risultati!H$5:H$15)&gt;=5,IF(Risultati!H13=3,1,0),0),IF(COUNT(Risultati!I$5:I$15)&gt;=5,IF(Risultati!I13=3,1,0),0),IF(COUNT(Risultati!J$5:J$15)&gt;=5,IF(Risultati!J13=3,1,0),0),IF(COUNT(Risultati!K$5:K$15)&gt;=5,IF(Risultati!K13=3,1,0),0),IF(COUNT(Risultati!L$5:L$15)&gt;=5,IF(Risultati!L13=3,1,0),0),IF(COUNT(Risultati!M$5:M$15)&gt;=5,IF(Risultati!M13=3,1,0),0))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G13" s="8">
         <f>SUM(Dettaglio!B13:M13)</f>
-        <v>0</v>
-      </c>
-      <c r="H13" s="8" t="str">
+        <v>20</v>
+      </c>
+      <c r="H13" s="8">
         <f>IF(COUNT(Dettaglio!B13:M13)=0,"—",SMALL(Dettaglio!B13:M13,1))</f>
-        <v>—</v>
+        <v>20</v>
       </c>
       <c r="I13" s="8" t="str">
         <f>IF(COUNT(Dettaglio!B13:M13)&lt;2,"—",SMALL(Dettaglio!B13:M13,2))</f>
@@ -1745,9 +1745,9 @@
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A14" s="8" t="str">
-        <f>IF(COUNT(Dettaglio!B14:M14)=0,"—",_xludf.RANK.EQ(J14,$J$5:$J$15,0))</f>
-        <v>—</v>
+      <c r="A14" s="8" t="e">
+        <f ca="1">IF(COUNT(Dettaglio!B14:M14)=0,"—",_xludf.RANK.EQ(J14,$J$5:$J$15,0))</f>
+        <v>#NAME?</v>
       </c>
       <c r="B14" s="3" t="s">
         <v>13</v>
@@ -1772,9 +1772,9 @@
         <f>SUM(Dettaglio!B14:M14)</f>
         <v>0</v>
       </c>
-      <c r="H14" s="8" t="str">
+      <c r="H14" s="8">
         <f>IF(COUNT(Dettaglio!B14:M14)=0,"—",SMALL(Dettaglio!B14:M14,1))</f>
-        <v>—</v>
+        <v>0</v>
       </c>
       <c r="I14" s="8" t="str">
         <f>IF(COUNT(Dettaglio!B14:M14)&lt;2,"—",SMALL(Dettaglio!B14:M14,2))</f>
@@ -1786,9 +1786,9 @@
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A15" s="8" t="str">
-        <f>IF(COUNT(Dettaglio!B15:M15)=0,"—",_xludf.RANK.EQ(J15,$J$5:$J$15,0))</f>
-        <v>—</v>
+      <c r="A15" s="8" t="e">
+        <f ca="1">IF(COUNT(Dettaglio!B15:M15)=0,"—",_xludf.RANK.EQ(J15,$J$5:$J$15,0))</f>
+        <v>#NAME?</v>
       </c>
       <c r="B15" s="3" t="s">
         <v>14</v>
@@ -1813,9 +1813,9 @@
         <f>SUM(Dettaglio!B15:M15)</f>
         <v>0</v>
       </c>
-      <c r="H15" s="8" t="str">
+      <c r="H15" s="8">
         <f>IF(COUNT(Dettaglio!B15:M15)=0,"—",SMALL(Dettaglio!B15:M15,1))</f>
-        <v>—</v>
+        <v>0</v>
       </c>
       <c r="I15" s="8" t="str">
         <f>IF(COUNT(Dettaglio!B15:M15)&lt;2,"—",SMALL(Dettaglio!B15:M15,2))</f>
@@ -1936,9 +1936,9 @@
       <c r="A5" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="8" t="str">
+      <c r="B5" s="8">
         <f>IF(COUNT(Risultati!B$5:B$15)&gt;=5,IF(Risultati!B5="",0,5+INDEX(Regole!$D$2:$D$13,Risultati!B5)+IF(Risultati!B$17=$A5,INDEX(Regole!$D$2:$D$13,Risultati!B5),0)),"")</f>
-        <v/>
+        <v>15</v>
       </c>
       <c r="C5" s="8" t="str">
         <f>IF(COUNT(Risultati!C$5:C$15)&gt;=5,IF(Risultati!C5="",0,5+INDEX(Regole!$D$2:$D$13,Risultati!C5)+IF(Risultati!C$17=$A5,INDEX(Regole!$D$2:$D$13,Risultati!C5),0)),"")</f>
@@ -1989,9 +1989,9 @@
       <c r="A6" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="8" t="str">
+      <c r="B6" s="8">
         <f>IF(COUNT(Risultati!B$5:B$15)&gt;=5,IF(Risultati!B6="",0,5+INDEX(Regole!$D$2:$D$13,Risultati!B6)+IF(Risultati!B$17=$A6,INDEX(Regole!$D$2:$D$13,Risultati!B6),0)),"")</f>
-        <v/>
+        <v>17</v>
       </c>
       <c r="C6" s="8" t="str">
         <f>IF(COUNT(Risultati!C$5:C$15)&gt;=5,IF(Risultati!C6="",0,5+INDEX(Regole!$D$2:$D$13,Risultati!C6)+IF(Risultati!C$17=$A6,INDEX(Regole!$D$2:$D$13,Risultati!C6),0)),"")</f>
@@ -2042,9 +2042,9 @@
       <c r="A7" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B7" s="8" t="str">
+      <c r="B7" s="8">
         <f>IF(COUNT(Risultati!B$5:B$15)&gt;=5,IF(Risultati!B7="",0,5+INDEX(Regole!$D$2:$D$13,Risultati!B7)+IF(Risultati!B$17=$A7,INDEX(Regole!$D$2:$D$13,Risultati!B7),0)),"")</f>
-        <v/>
+        <v>30</v>
       </c>
       <c r="C7" s="8" t="str">
         <f>IF(COUNT(Risultati!C$5:C$15)&gt;=5,IF(Risultati!C7="",0,5+INDEX(Regole!$D$2:$D$13,Risultati!C7)+IF(Risultati!C$17=$A7,INDEX(Regole!$D$2:$D$13,Risultati!C7),0)),"")</f>
@@ -2095,9 +2095,9 @@
       <c r="A8" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="B8" s="8" t="str">
+      <c r="B8" s="8">
         <f>IF(COUNT(Risultati!B$5:B$15)&gt;=5,IF(Risultati!B8="",0,5+INDEX(Regole!$D$2:$D$13,Risultati!B8)+IF(Risultati!B$17=$A8,INDEX(Regole!$D$2:$D$13,Risultati!B8),0)),"")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="C8" s="8" t="str">
         <f>IF(COUNT(Risultati!C$5:C$15)&gt;=5,IF(Risultati!C8="",0,5+INDEX(Regole!$D$2:$D$13,Risultati!C8)+IF(Risultati!C$17=$A8,INDEX(Regole!$D$2:$D$13,Risultati!C8),0)),"")</f>
@@ -2148,9 +2148,9 @@
       <c r="A9" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B9" s="8" t="str">
+      <c r="B9" s="8">
         <f>IF(COUNT(Risultati!B$5:B$15)&gt;=5,IF(Risultati!B9="",0,5+INDEX(Regole!$D$2:$D$13,Risultati!B9)+IF(Risultati!B$17=$A9,INDEX(Regole!$D$2:$D$13,Risultati!B9),0)),"")</f>
-        <v/>
+        <v>13</v>
       </c>
       <c r="C9" s="8" t="str">
         <f>IF(COUNT(Risultati!C$5:C$15)&gt;=5,IF(Risultati!C9="",0,5+INDEX(Regole!$D$2:$D$13,Risultati!C9)+IF(Risultati!C$17=$A9,INDEX(Regole!$D$2:$D$13,Risultati!C9),0)),"")</f>
@@ -2201,9 +2201,9 @@
       <c r="A10" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B10" s="8" t="str">
+      <c r="B10" s="8">
         <f>IF(COUNT(Risultati!B$5:B$15)&gt;=5,IF(Risultati!B10="",0,5+INDEX(Regole!$D$2:$D$13,Risultati!B10)+IF(Risultati!B$17=$A10,INDEX(Regole!$D$2:$D$13,Risultati!B10),0)),"")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="C10" s="8" t="str">
         <f>IF(COUNT(Risultati!C$5:C$15)&gt;=5,IF(Risultati!C10="",0,5+INDEX(Regole!$D$2:$D$13,Risultati!C10)+IF(Risultati!C$17=$A10,INDEX(Regole!$D$2:$D$13,Risultati!C10),0)),"")</f>
@@ -2254,9 +2254,9 @@
       <c r="A11" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="B11" s="8" t="str">
+      <c r="B11" s="8">
         <f>IF(COUNT(Risultati!B$5:B$15)&gt;=5,IF(Risultati!B11="",0,5+INDEX(Regole!$D$2:$D$13,Risultati!B11)+IF(Risultati!B$17=$A11,INDEX(Regole!$D$2:$D$13,Risultati!B11),0)),"")</f>
-        <v/>
+        <v>23</v>
       </c>
       <c r="C11" s="8" t="str">
         <f>IF(COUNT(Risultati!C$5:C$15)&gt;=5,IF(Risultati!C11="",0,5+INDEX(Regole!$D$2:$D$13,Risultati!C11)+IF(Risultati!C$17=$A11,INDEX(Regole!$D$2:$D$13,Risultati!C11),0)),"")</f>
@@ -2307,9 +2307,9 @@
       <c r="A12" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="B12" s="8" t="str">
+      <c r="B12" s="8">
         <f>IF(COUNT(Risultati!B$5:B$15)&gt;=5,IF(Risultati!B12="",0,5+INDEX(Regole!$D$2:$D$13,Risultati!B12)+IF(Risultati!B$17=$A12,INDEX(Regole!$D$2:$D$13,Risultati!B12),0)),"")</f>
-        <v/>
+        <v>11</v>
       </c>
       <c r="C12" s="8" t="str">
         <f>IF(COUNT(Risultati!C$5:C$15)&gt;=5,IF(Risultati!C12="",0,5+INDEX(Regole!$D$2:$D$13,Risultati!C12)+IF(Risultati!C$17=$A12,INDEX(Regole!$D$2:$D$13,Risultati!C12),0)),"")</f>
@@ -2360,9 +2360,9 @@
       <c r="A13" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="B13" s="8" t="str">
+      <c r="B13" s="8">
         <f>IF(COUNT(Risultati!B$5:B$15)&gt;=5,IF(Risultati!B13="",0,5+INDEX(Regole!$D$2:$D$13,Risultati!B13)+IF(Risultati!B$17=$A13,INDEX(Regole!$D$2:$D$13,Risultati!B13),0)),"")</f>
-        <v/>
+        <v>20</v>
       </c>
       <c r="C13" s="8" t="str">
         <f>IF(COUNT(Risultati!C$5:C$15)&gt;=5,IF(Risultati!C13="",0,5+INDEX(Regole!$D$2:$D$13,Risultati!C13)+IF(Risultati!C$17=$A13,INDEX(Regole!$D$2:$D$13,Risultati!C13),0)),"")</f>
@@ -2413,9 +2413,9 @@
       <c r="A14" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="B14" s="8" t="str">
+      <c r="B14" s="8">
         <f>IF(COUNT(Risultati!B$5:B$15)&gt;=5,IF(Risultati!B14="",0,5+INDEX(Regole!$D$2:$D$13,Risultati!B14)+IF(Risultati!B$17=$A14,INDEX(Regole!$D$2:$D$13,Risultati!B14),0)),"")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="C14" s="8" t="str">
         <f>IF(COUNT(Risultati!C$5:C$15)&gt;=5,IF(Risultati!C14="",0,5+INDEX(Regole!$D$2:$D$13,Risultati!C14)+IF(Risultati!C$17=$A14,INDEX(Regole!$D$2:$D$13,Risultati!C14),0)),"")</f>
@@ -2466,9 +2466,9 @@
       <c r="A15" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="B15" s="8" t="str">
+      <c r="B15" s="8">
         <f>IF(COUNT(Risultati!B$5:B$15)&gt;=5,IF(Risultati!B15="",0,5+INDEX(Regole!$D$2:$D$13,Risultati!B15)+IF(Risultati!B$17=$A15,INDEX(Regole!$D$2:$D$13,Risultati!B15),0)),"")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="C15" s="8" t="str">
         <f>IF(COUNT(Risultati!C$5:C$15)&gt;=5,IF(Risultati!C15="",0,5+INDEX(Regole!$D$2:$D$13,Risultati!C15)+IF(Risultati!C$17=$A15,INDEX(Regole!$D$2:$D$13,Risultati!C15),0)),"")</f>
